--- a/docs/review-checklist.xlsx
+++ b/docs/review-checklist.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="345">
   <si>
     <t>No.</t>
   </si>
@@ -59,10 +59,166 @@
     <t>指摘事項・コメント</t>
   </si>
   <si>
+    <t>cv-joint</t>
+  </si>
+  <si>
+    <t>CVジョイント</t>
+  </si>
+  <si>
+    <t>自動車部品</t>
+  </si>
+  <si>
+    <t>シーブイジョイント</t>
+  </si>
+  <si>
+    <t>Constant Velocity Joint</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>ecu</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t>イーシーユー</t>
+  </si>
+  <si>
+    <t>Electronic Control Unit</t>
+  </si>
+  <si>
+    <t>egr-valve</t>
+  </si>
+  <si>
+    <t>EGRバルブ</t>
+  </si>
+  <si>
+    <t>イージーアールバルブ</t>
+  </si>
+  <si>
+    <t>EGR Valve</t>
+  </si>
+  <si>
+    <t>fuel-injector</t>
+  </si>
+  <si>
+    <t>インジェクター</t>
+  </si>
+  <si>
+    <t>Fuel Injector</t>
+  </si>
+  <si>
+    <t>intercooler</t>
+  </si>
+  <si>
+    <t>インタークーラー</t>
+  </si>
+  <si>
+    <t>Intercooler</t>
+  </si>
+  <si>
+    <t>oil-pump</t>
+  </si>
+  <si>
+    <t>オイルポンプ</t>
+  </si>
+  <si>
+    <t>Oil Pump</t>
+  </si>
+  <si>
+    <t>suspension</t>
+  </si>
+  <si>
+    <t>サスペンション</t>
+  </si>
+  <si>
+    <t>Suspension</t>
+  </si>
+  <si>
+    <t>stabilizer-bar</t>
+  </si>
+  <si>
+    <t>スタビライザー</t>
+  </si>
+  <si>
+    <t>Anti-Roll Bar</t>
+  </si>
+  <si>
+    <t>throttle-body</t>
+  </si>
+  <si>
+    <t>スロットルボディ</t>
+  </si>
+  <si>
+    <t>Throttle Body</t>
+  </si>
+  <si>
+    <t>damper</t>
+  </si>
+  <si>
+    <t>ダンパー</t>
+  </si>
+  <si>
+    <t>Shock Absorber</t>
+  </si>
+  <si>
+    <t>drive-shaft</t>
+  </si>
+  <si>
+    <t>ドライブシャフト</t>
+  </si>
+  <si>
+    <t>Drive Shaft</t>
+  </si>
+  <si>
+    <t>brake-caliper</t>
+  </si>
+  <si>
+    <t>ブレーキキャリパー</t>
+  </si>
+  <si>
+    <t>Brake Caliper</t>
+  </si>
+  <si>
+    <t>bearing</t>
+  </si>
+  <si>
+    <t>ベアリング</t>
+  </si>
+  <si>
+    <t>Bearing</t>
+  </si>
+  <si>
+    <t>wheel-hub</t>
+  </si>
+  <si>
+    <t>ホイールハブ</t>
+  </si>
+  <si>
+    <t>Wheel Hub</t>
+  </si>
+  <si>
+    <t>catalytic-converter</t>
+  </si>
+  <si>
+    <t>三元触媒</t>
+  </si>
+  <si>
+    <t>サンゲンショクバイ</t>
+  </si>
+  <si>
+    <t>Three-Way Catalytic Converter</t>
+  </si>
+  <si>
     <t>csms</t>
   </si>
   <si>
-    <t>CSMS（サイバーセキュリティ管理システム）</t>
+    <t>CSMS</t>
   </si>
   <si>
     <t>サイバーセキュリティ</t>
@@ -74,16 +230,10 @@
     <t>Cyber Security Management System</t>
   </si>
   <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>hsm</t>
   </si>
   <si>
-    <t>HSM（ハードウェアセキュリティモジュール）</t>
+    <t>HSM</t>
   </si>
   <si>
     <t>エイチエスエム</t>
@@ -92,22 +242,16 @@
     <t>Hardware Security Module</t>
   </si>
   <si>
-    <t>2026-03-12</t>
-  </si>
-  <si>
     <t>ids-ips</t>
   </si>
   <si>
-    <t>IDS/IPS（侵入検知/防御システム）</t>
+    <t>IDS/IPS</t>
   </si>
   <si>
     <t>アイディーエスアイピーエス</t>
   </si>
   <si>
-    <t>Intrusion Detection System / Intrusion Prevention System</t>
-  </si>
-  <si>
-    <t>2026-03-09</t>
+    <t>Intrusion Detection/Prevention System</t>
   </si>
   <si>
     <t>iso-sae-21434</t>
@@ -116,19 +260,16 @@
     <t>ISO/SAE 21434</t>
   </si>
   <si>
-    <t>アイエスオーエスエーイーニイチヨンサンヨン</t>
+    <t>アイエスオーエスエーイー21434</t>
   </si>
   <si>
     <t>ISO/SAE 21434 Road Vehicles - Cybersecurity Engineering</t>
   </si>
   <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
     <t>pki</t>
   </si>
   <si>
-    <t>PKI（公開鍵基盤）</t>
+    <t>PKI</t>
   </si>
   <si>
     <t>ピーケーアイ</t>
@@ -137,28 +278,22 @@
     <t>Public Key Infrastructure</t>
   </si>
   <si>
-    <t>2026-03-13</t>
-  </si>
-  <si>
     <t>secoc</t>
   </si>
   <si>
-    <t>SecOC（Secure Onboard Communication）</t>
-  </si>
-  <si>
-    <t>セックオーシー</t>
+    <t>SecOC</t>
+  </si>
+  <si>
+    <t>セクオーシー</t>
   </si>
   <si>
     <t>Secure Onboard Communication</t>
   </si>
   <si>
-    <t>2026-03-11</t>
-  </si>
-  <si>
     <t>sums</t>
   </si>
   <si>
-    <t>SUMS（ソフトウェアアップデート管理システム）</t>
+    <t>SUMS</t>
   </si>
   <si>
     <t>サムス</t>
@@ -167,37 +302,28 @@
     <t>Software Update Management System</t>
   </si>
   <si>
-    <t>2026-03-03</t>
-  </si>
-  <si>
     <t>tara</t>
   </si>
   <si>
-    <t>TARA（脅威分析とリスク評価）</t>
-  </si>
-  <si>
-    <t>タラ</t>
+    <t>TARA</t>
+  </si>
+  <si>
+    <t>ターラ</t>
   </si>
   <si>
     <t>Threat Analysis and Risk Assessment</t>
   </si>
   <si>
-    <t>2026-03-05</t>
-  </si>
-  <si>
-    <t>vehicle-soc</t>
-  </si>
-  <si>
-    <t>V-SOC（車両セキュリティオペレーションセンター）</t>
-  </si>
-  <si>
-    <t>ブイソック</t>
-  </si>
-  <si>
-    <t>Vehicle Security Operations Center</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
+    <t>vlan-separation</t>
+  </si>
+  <si>
+    <t>VLAN分離</t>
+  </si>
+  <si>
+    <t>ブイランブンリ</t>
+  </si>
+  <si>
+    <t>VLAN Separation</t>
   </si>
   <si>
     <t>secure-ota</t>
@@ -212,9 +338,6 @@
     <t>Secure Over-The-Air Update</t>
   </si>
   <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
     <t>secure-boot</t>
   </si>
   <si>
@@ -224,55 +347,28 @@
     <t>Secure Boot</t>
   </si>
   <si>
-    <t>2026-03-07</t>
-  </si>
-  <si>
-    <t>vlan-separation</t>
-  </si>
-  <si>
-    <t>ネットワーク分離（VLAN/ゾーン分割）</t>
-  </si>
-  <si>
-    <t>ネットワークブンリ</t>
-  </si>
-  <si>
-    <t>Network Segmentation / VLAN</t>
-  </si>
-  <si>
-    <t>2026-03-14</t>
-  </si>
-  <si>
     <t>fuzz-testing</t>
   </si>
   <si>
-    <t>ファジングテスト</t>
-  </si>
-  <si>
-    <t>Fuzz Testing / Fuzzing</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
+    <t>ファズテスト</t>
+  </si>
+  <si>
+    <t>Fuzz Testing</t>
   </si>
   <si>
     <t>penetration-testing</t>
   </si>
   <si>
-    <t>ペネトレーションテスト（侵入テスト）</t>
-  </si>
-  <si>
     <t>ペネトレーションテスト</t>
   </si>
   <si>
     <t>Penetration Testing</t>
   </si>
   <si>
-    <t>2026-03-15</t>
-  </si>
-  <si>
     <t>defense-in-depth</t>
   </si>
   <si>
-    <t>多層防御（Defense in Depth）</t>
+    <t>多層防御</t>
   </si>
   <si>
     <t>タソウボウギョ</t>
@@ -281,196 +377,154 @@
     <t>Defense in Depth</t>
   </si>
   <si>
-    <t>2026-03-04</t>
+    <t>sid-0x10</t>
+  </si>
+  <si>
+    <t>SID 0x10 DiagnosticSessionControl</t>
+  </si>
+  <si>
+    <t>診断通信</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x10</t>
+  </si>
+  <si>
+    <t>Diagnostic Session Control</t>
+  </si>
+  <si>
+    <t>sid-0x11</t>
+  </si>
+  <si>
+    <t>SID 0x11 ECUReset</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x11</t>
+  </si>
+  <si>
+    <t>ECU Reset</t>
+  </si>
+  <si>
+    <t>sid-0x14</t>
+  </si>
+  <si>
+    <t>SID 0x14 ClearDiagnosticInformation</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x14</t>
+  </si>
+  <si>
+    <t>Clear Diagnostic Information</t>
+  </si>
+  <si>
+    <t>sid-0x19</t>
+  </si>
+  <si>
+    <t>SID 0x19 ReadDTCInformation</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x19</t>
+  </si>
+  <si>
+    <t>Read DTC Information</t>
+  </si>
+  <si>
+    <t>sid-0x22</t>
+  </si>
+  <si>
+    <t>SID 0x22 ReadDataByIdentifier</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x22</t>
+  </si>
+  <si>
+    <t>Read Data By Identifier</t>
+  </si>
+  <si>
+    <t>sid-0x27</t>
+  </si>
+  <si>
+    <t>SID 0x27 SecurityAccess</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x27</t>
+  </si>
+  <si>
+    <t>Security Access</t>
+  </si>
+  <si>
+    <t>sid-0x2e</t>
+  </si>
+  <si>
+    <t>SID 0x2E WriteDataByIdentifier</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x2E</t>
+  </si>
+  <si>
+    <t>Write Data By Identifier</t>
+  </si>
+  <si>
+    <t>sid-0x31</t>
+  </si>
+  <si>
+    <t>SID 0x31 RoutineControl</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x31</t>
+  </si>
+  <si>
+    <t>Routine Control</t>
+  </si>
+  <si>
+    <t>sid-0x34-36-37</t>
+  </si>
+  <si>
+    <t>SID 0x34/36/37 リプログラミング</t>
+  </si>
+  <si>
+    <t>リプログラミングサービス</t>
+  </si>
+  <si>
+    <t>RequestDownload / TransferData / RequestTransferExit</t>
+  </si>
+  <si>
+    <t>sid-0x3e</t>
+  </si>
+  <si>
+    <t>SID 0x3E TesterPresent</t>
+  </si>
+  <si>
+    <t>サービスアイディー0x3E</t>
+  </si>
+  <si>
+    <t>Tester Present</t>
+  </si>
+  <si>
+    <t>uds</t>
+  </si>
+  <si>
+    <t>UDS</t>
+  </si>
+  <si>
+    <t>ユーディーエス</t>
+  </si>
+  <si>
+    <t>Unified Diagnostic Services (ISO 14229)</t>
   </si>
   <si>
     <t>negative-response</t>
   </si>
   <si>
-    <t>NRC（否定応答コード）</t>
-  </si>
-  <si>
-    <t>診断通信</t>
-  </si>
-  <si>
-    <t>エヌアールシー</t>
-  </si>
-  <si>
-    <t>Negative Response Code</t>
-  </si>
-  <si>
-    <t>2026-04-10</t>
-  </si>
-  <si>
-    <t>sid-0x10</t>
-  </si>
-  <si>
-    <t>SID 0x10（DiagnosticSessionControl）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスジュウ</t>
-  </si>
-  <si>
-    <t>DiagnosticSessionControl (SID 0x10)</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>sid-0x11</t>
-  </si>
-  <si>
-    <t>SID 0x11（ECUReset）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスジュウイチ</t>
-  </si>
-  <si>
-    <t>ECUReset (SID 0x11)</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>sid-0x14</t>
-  </si>
-  <si>
-    <t>SID 0x14（ClearDiagnosticInformation）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスジュウヨン</t>
-  </si>
-  <si>
-    <t>ClearDiagnosticInformation (SID 0x14)</t>
-  </si>
-  <si>
-    <t>2026-04-02</t>
-  </si>
-  <si>
-    <t>sid-0x19</t>
-  </si>
-  <si>
-    <t>SID 0x19（ReadDTCInformation）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスジュウキュウ</t>
-  </si>
-  <si>
-    <t>ReadDTCInformation (SID 0x19)</t>
-  </si>
-  <si>
-    <t>2026-04-03</t>
-  </si>
-  <si>
-    <t>sid-0x22</t>
-  </si>
-  <si>
-    <t>SID 0x22（ReadDataByIdentifier）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスニジュウニ</t>
-  </si>
-  <si>
-    <t>ReadDataByIdentifier (SID 0x22)</t>
-  </si>
-  <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
-    <t>sid-0x27</t>
-  </si>
-  <si>
-    <t>SID 0x27（SecurityAccess）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスニジュウナナ</t>
-  </si>
-  <si>
-    <t>SecurityAccess (SID 0x27)</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>sid-0x2e</t>
-  </si>
-  <si>
-    <t>SID 0x2E（WriteDataByIdentifier）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスニジュウハチイー</t>
-  </si>
-  <si>
-    <t>WriteDataByIdentifier (SID 0x2E)</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>sid-0x31</t>
-  </si>
-  <si>
-    <t>SID 0x31（RoutineControl）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスサンジュウイチ</t>
-  </si>
-  <si>
-    <t>RoutineControl (SID 0x31)</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>sid-0x34-36-37</t>
-  </si>
-  <si>
-    <t>SID 0x34/0x36/0x37（ダウンロード転送）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスサンヨン</t>
-  </si>
-  <si>
-    <t>RequestDownload / TransferData / RequestTransferExit</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
-  </si>
-  <si>
-    <t>sid-0x3e</t>
-  </si>
-  <si>
-    <t>SID 0x3E（TesterPresent）</t>
-  </si>
-  <si>
-    <t>エスアイディーゼロエックスサンイー</t>
-  </si>
-  <si>
-    <t>TesterPresent (SID 0x3E)</t>
-  </si>
-  <si>
-    <t>2026-04-09</t>
-  </si>
-  <si>
-    <t>uds</t>
-  </si>
-  <si>
-    <t>UDS（統一診断サービス）</t>
-  </si>
-  <si>
-    <t>ユーディーエス</t>
-  </si>
-  <si>
-    <t>Unified Diagnostic Services (ISO 14229)</t>
-  </si>
-  <si>
-    <t>2026-03-30</t>
+    <t>ネガティブレスポンス</t>
+  </si>
+  <si>
+    <t>Negative Response Code (NRC)</t>
   </si>
   <si>
     <t>asil</t>
   </si>
   <si>
-    <t>ASIL（自動車安全度水準）</t>
+    <t>ASIL</t>
   </si>
   <si>
     <t>機能安全</t>
@@ -482,9 +536,6 @@
     <t>Automotive Safety Integrity Level</t>
   </si>
   <si>
-    <t>2026-03-18</t>
-  </si>
-  <si>
     <t>asil-decomposition</t>
   </si>
   <si>
@@ -497,169 +548,163 @@
     <t>ASIL Decomposition</t>
   </si>
   <si>
-    <t>2026-03-22</t>
-  </si>
-  <si>
     <t>controllability</t>
   </si>
   <si>
-    <t>C値（制御可能性）</t>
-  </si>
-  <si>
-    <t>シーチ</t>
-  </si>
-  <si>
-    <t>Controllability (C0-C3)</t>
-  </si>
-  <si>
-    <t>2026-03-21</t>
+    <t>Controllability（制御可能性）</t>
+  </si>
+  <si>
+    <t>コントローラビリティ</t>
+  </si>
+  <si>
+    <t>Controllability</t>
   </si>
   <si>
     <t>exposure</t>
   </si>
   <si>
-    <t>E値（暴露度）</t>
-  </si>
-  <si>
-    <t>イーチ</t>
-  </si>
-  <si>
-    <t>Exposure (E0-E4)</t>
-  </si>
-  <si>
-    <t>2026-03-20</t>
+    <t>Exposure（頻度）</t>
+  </si>
+  <si>
+    <t>エクスポージャー</t>
+  </si>
+  <si>
+    <t>Exposure</t>
+  </si>
+  <si>
+    <t>fmea</t>
+  </si>
+  <si>
+    <t>FMEA</t>
+  </si>
+  <si>
+    <t>エフエムイーエー</t>
+  </si>
+  <si>
+    <t>Failure Mode and Effects Analysis</t>
+  </si>
+  <si>
+    <t>fta</t>
+  </si>
+  <si>
+    <t>FTA</t>
+  </si>
+  <si>
+    <t>エフティーエー</t>
+  </si>
+  <si>
+    <t>Fault Tree Analysis</t>
+  </si>
+  <si>
+    <t>hara</t>
+  </si>
+  <si>
+    <t>HARA</t>
+  </si>
+  <si>
+    <t>ハラ</t>
+  </si>
+  <si>
+    <t>Hazard Analysis and Risk Assessment</t>
+  </si>
+  <si>
+    <t>iso-26262</t>
+  </si>
+  <si>
+    <t>ISO 26262</t>
+  </si>
+  <si>
+    <t>アイエスオー26262</t>
+  </si>
+  <si>
+    <t>ISO 26262 Road Vehicles - Functional Safety</t>
+  </si>
+  <si>
+    <t>severity</t>
+  </si>
+  <si>
+    <t>Severity（重大度）</t>
+  </si>
+  <si>
+    <t>セベリティ</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>sotif</t>
+  </si>
+  <si>
+    <t>SOTIF</t>
+  </si>
+  <si>
+    <t>ソティフ</t>
+  </si>
+  <si>
+    <t>Safety Of The Intended Functionality (ISO 21448)</t>
+  </si>
+  <si>
+    <t>safety-case</t>
+  </si>
+  <si>
+    <t>セーフティケース</t>
+  </si>
+  <si>
+    <t>Safety Case</t>
+  </si>
+  <si>
+    <t>safety-goal</t>
+  </si>
+  <si>
+    <t>セーフティゴール</t>
+  </si>
+  <si>
+    <t>Safety Goal</t>
   </si>
   <si>
     <t>freedom-from-interference</t>
   </si>
   <si>
-    <t>FFI（干渉からの自由）</t>
-  </si>
-  <si>
-    <t>エフエフアイ</t>
-  </si>
-  <si>
-    <t>Freedom From Interference</t>
-  </si>
-  <si>
-    <t>2026-03-28</t>
-  </si>
-  <si>
-    <t>fmea</t>
-  </si>
-  <si>
-    <t>FMEA（故障モード影響解析）</t>
-  </si>
-  <si>
-    <t>エフエムイーエー</t>
-  </si>
-  <si>
-    <t>Failure Mode and Effects Analysis</t>
-  </si>
-  <si>
-    <t>2026-03-25</t>
-  </si>
-  <si>
-    <t>fta</t>
-  </si>
-  <si>
-    <t>FTA（故障の木解析）</t>
-  </si>
-  <si>
-    <t>エフティーエー</t>
-  </si>
-  <si>
-    <t>Fault Tree Analysis</t>
-  </si>
-  <si>
-    <t>2026-03-26</t>
-  </si>
-  <si>
-    <t>hara</t>
-  </si>
-  <si>
-    <t>HARA（ハザード分析とリスク評価）</t>
-  </si>
-  <si>
-    <t>ハラ</t>
-  </si>
-  <si>
-    <t>Hazard Analysis and Risk Assessment</t>
-  </si>
-  <si>
-    <t>2026-03-24</t>
-  </si>
-  <si>
-    <t>iso-26262</t>
-  </si>
-  <si>
-    <t>ISO 26262</t>
-  </si>
-  <si>
-    <t>アイエスオーニロクニロクニ</t>
-  </si>
-  <si>
-    <t>ISO 26262 Road Vehicles - Functional Safety</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>sotif</t>
-  </si>
-  <si>
-    <t>SOTIF（意図した機能の安全性）</t>
-  </si>
-  <si>
-    <t>ソティフ</t>
-  </si>
-  <si>
-    <t>Safety of the Intended Functionality (ISO 21448)</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>severity</t>
-  </si>
-  <si>
-    <t>S値（重大度）</t>
-  </si>
-  <si>
-    <t>エスチ</t>
-  </si>
-  <si>
-    <t>Severity (S0-S3)</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
-  </si>
-  <si>
-    <t>safety-case</t>
-  </si>
-  <si>
-    <t>セーフティケース</t>
-  </si>
-  <si>
-    <t>Safety Case</t>
-  </si>
-  <si>
-    <t>2026-03-27</t>
-  </si>
-  <si>
-    <t>safety-goal</t>
-  </si>
-  <si>
-    <t>セーフティゴール（安全目標）</t>
-  </si>
-  <si>
-    <t>セーフティゴール</t>
-  </si>
-  <si>
-    <t>Safety Goal</t>
-  </si>
-  <si>
-    <t>2026-03-23</t>
+    <t>干渉からの自由</t>
+  </si>
+  <si>
+    <t>カンショウカラノジユウ</t>
+  </si>
+  <si>
+    <t>Freedom From Interference (FFI)</t>
+  </si>
+  <si>
+    <t>toyota-group</t>
+  </si>
+  <si>
+    <t>トヨタグループ</t>
+  </si>
+  <si>
+    <t>自動車関連メーカー</t>
+  </si>
+  <si>
+    <t>Toyota Group</t>
+  </si>
+  <si>
+    <t>honda-group</t>
+  </si>
+  <si>
+    <t>ホンダグループ</t>
+  </si>
+  <si>
+    <t>Honda Group</t>
+  </si>
+  <si>
+    <t>nissan-group</t>
+  </si>
+  <si>
+    <t>日産グループ（ルノー・日産・三菱アライアンス）</t>
+  </si>
+  <si>
+    <t>ニッサングループ</t>
+  </si>
+  <si>
+    <t>Renault-Nissan-Mitsubishi Alliance</t>
   </si>
   <si>
     <t>48v-mild-hybrid</t>
@@ -668,37 +713,19 @@
     <t>48Vマイルドハイブリッド</t>
   </si>
   <si>
-    <t>other</t>
+    <t>パワートレイン</t>
   </si>
   <si>
     <t>ヨンジュウハチボルトマイルドハイブリッド</t>
   </si>
   <si>
-    <t>48V Mild Hybrid System</t>
-  </si>
-  <si>
-    <t>2026-01-24</t>
-  </si>
-  <si>
-    <t>api</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>エーピーアイ</t>
-  </si>
-  <si>
-    <t>Application Programming Interface</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
+    <t>48V Mild Hybrid</t>
   </si>
   <si>
     <t>awd</t>
   </si>
   <si>
-    <t>AWD（全輪駆動）</t>
+    <t>AWD</t>
   </si>
   <si>
     <t>エーダブリューディー</t>
@@ -707,13 +734,10 @@
     <t>All-Wheel Drive</t>
   </si>
   <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
     <t>battery-management-system</t>
   </si>
   <si>
-    <t>BMS（バッテリーマネジメントシステム）</t>
+    <t>BMS</t>
   </si>
   <si>
     <t>ビーエムエス</t>
@@ -722,28 +746,10 @@
     <t>Battery Management System</t>
   </si>
   <si>
-    <t>2026-01-30</t>
-  </si>
-  <si>
-    <t>cookie</t>
-  </si>
-  <si>
-    <t>Cookie（クッキー）</t>
-  </si>
-  <si>
-    <t>クッキー</t>
-  </si>
-  <si>
-    <t>HTTP Cookie</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
-  </si>
-  <si>
     <t>cvt</t>
   </si>
   <si>
-    <t>CVT（無段変速機）</t>
+    <t>CVT</t>
   </si>
   <si>
     <t>シーブイティー</t>
@@ -752,70 +758,10 @@
     <t>Continuously Variable Transmission</t>
   </si>
   <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>cv-joint</t>
-  </si>
-  <si>
-    <t>CVジョイント（等速ジョイント）</t>
-  </si>
-  <si>
-    <t>シーブイジョイント</t>
-  </si>
-  <si>
-    <t>Constant Velocity Joint</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
-    <t>docker</t>
-  </si>
-  <si>
-    <t>Docker</t>
-  </si>
-  <si>
-    <t>ドッカー</t>
-  </si>
-  <si>
-    <t>2026-02-22</t>
-  </si>
-  <si>
-    <t>ecu</t>
-  </si>
-  <si>
-    <t>ECU（エンジンコントロールユニット）</t>
-  </si>
-  <si>
-    <t>イーシーユー</t>
-  </si>
-  <si>
-    <t>Engine Control Unit</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>egr-valve</t>
-  </si>
-  <si>
-    <t>EGRバルブ</t>
-  </si>
-  <si>
-    <t>イージーアールバルブ</t>
-  </si>
-  <si>
-    <t>Exhaust Gas Recirculation Valve</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
     <t>e-axle</t>
   </si>
   <si>
-    <t>eアクスル（電動アクスル）</t>
+    <t>eアクスル</t>
   </si>
   <si>
     <t>イーアクスル</t>
@@ -824,58 +770,10 @@
     <t>Electric Axle</t>
   </si>
   <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>nsk</t>
-  </si>
-  <si>
-    <t>NSK（日本精工）</t>
-  </si>
-  <si>
-    <t>エヌエスケー</t>
-  </si>
-  <si>
-    <t>NSK Ltd.</t>
-  </si>
-  <si>
-    <t>2026-02-08</t>
-  </si>
-  <si>
-    <t>sql</t>
-  </si>
-  <si>
-    <t>SQL</t>
-  </si>
-  <si>
-    <t>エスキューエル</t>
-  </si>
-  <si>
-    <t>Structured Query Language</t>
-  </si>
-  <si>
-    <t>2026-02-24</t>
-  </si>
-  <si>
-    <t>subaru</t>
-  </si>
-  <si>
-    <t>SUBARU（スバル）</t>
-  </si>
-  <si>
-    <t>スバル</t>
-  </si>
-  <si>
-    <t>SUBARU Corporation</t>
-  </si>
-  <si>
-    <t>2026-01-31</t>
-  </si>
-  <si>
     <t>ths</t>
   </si>
   <si>
-    <t>THS（トヨタハイブリッドシステム）</t>
+    <t>THS</t>
   </si>
   <si>
     <t>ティーエイチエス</t>
@@ -884,58 +782,13 @@
     <t>Toyota Hybrid System</t>
   </si>
   <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>aisin</t>
-  </si>
-  <si>
-    <t>アイシン</t>
-  </si>
-  <si>
-    <t>AISIN Corporation</t>
-  </si>
-  <si>
-    <t>2026-02-04</t>
-  </si>
-  <si>
     <t>atkinson-cycle</t>
   </si>
   <si>
-    <t>アトキンソンサイクルエンジン</t>
-  </si>
-  <si>
-    <t>Atkinson Cycle Engine</t>
-  </si>
-  <si>
-    <t>2026-01-27</t>
-  </si>
-  <si>
-    <t>fuel-injector</t>
-  </si>
-  <si>
-    <t>インジェクター（燃料噴射装置）</t>
-  </si>
-  <si>
-    <t>インジェクター</t>
-  </si>
-  <si>
-    <t>Fuel Injector</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>intercooler</t>
-  </si>
-  <si>
-    <t>インタークーラー</t>
-  </si>
-  <si>
-    <t>Intercooler</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
+    <t>アトキンソンサイクル</t>
+  </si>
+  <si>
+    <t>Atkinson Cycle</t>
   </si>
   <si>
     <t>inverter</t>
@@ -947,243 +800,33 @@
     <t>Inverter</t>
   </si>
   <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>oil-pump</t>
-  </si>
-  <si>
-    <t>オイルポンプ</t>
-  </si>
-  <si>
-    <t>Oil Pump</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>continental</t>
-  </si>
-  <si>
-    <t>コンチネンタル</t>
-  </si>
-  <si>
-    <t>Continental AG</t>
-  </si>
-  <si>
-    <t>2026-02-06</t>
-  </si>
-  <si>
-    <t>suspension</t>
-  </si>
-  <si>
-    <t>サスペンション</t>
-  </si>
-  <si>
-    <t>Suspension</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>jtekt</t>
-  </si>
-  <si>
-    <t>ジェイテクト</t>
-  </si>
-  <si>
-    <t>JTEKT Corporation</t>
-  </si>
-  <si>
-    <t>2026-02-07</t>
-  </si>
-  <si>
-    <t>stabilizer-bar</t>
-  </si>
-  <si>
-    <t>スタビライザー</t>
-  </si>
-  <si>
-    <t>Stabilizer Bar / Anti-Roll Bar</t>
-  </si>
-  <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
-    <t>throttle-body</t>
-  </si>
-  <si>
-    <t>スロットルボディ</t>
-  </si>
-  <si>
-    <t>Throttle Body</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
     <t>turbocharger</t>
   </si>
   <si>
-    <t>ターボチャージャー（過給機）</t>
-  </si>
-  <si>
     <t>ターボチャージャー</t>
   </si>
   <si>
     <t>Turbocharger</t>
   </si>
   <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>damper</t>
-  </si>
-  <si>
-    <t>ダンパー（ショックアブソーバー）</t>
-  </si>
-  <si>
-    <t>ダンパー</t>
-  </si>
-  <si>
-    <t>Shock Absorber / Damper</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
     <t>differential</t>
   </si>
   <si>
-    <t>デファレンシャルギア（差動装置）</t>
-  </si>
-  <si>
     <t>デファレンシャルギア</t>
   </si>
   <si>
     <t>Differential Gear</t>
   </si>
   <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>denso</t>
-  </si>
-  <si>
-    <t>デンソー</t>
-  </si>
-  <si>
-    <t>DENSO Corporation</t>
-  </si>
-  <si>
-    <t>2026-02-03</t>
-  </si>
-  <si>
-    <t>toyota</t>
-  </si>
-  <si>
-    <t>トヨタ自動車</t>
-  </si>
-  <si>
-    <t>トヨタジドウシャ</t>
-  </si>
-  <si>
-    <t>Toyota Motor Corporation</t>
-  </si>
-  <si>
-    <t>2026-02-10</t>
-  </si>
-  <si>
-    <t>drive-shaft</t>
-  </si>
-  <si>
-    <t>ドライブシャフト</t>
-  </si>
-  <si>
-    <t>Drive Shaft</t>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>firewall</t>
-  </si>
-  <si>
-    <t>ファイアウォール</t>
-  </si>
-  <si>
-    <t>Firewall</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
-  </si>
-  <si>
-    <t>brake-caliper</t>
-  </si>
-  <si>
-    <t>ブレーキキャリパー</t>
-  </si>
-  <si>
-    <t>Brake Caliper</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>bearing</t>
-  </si>
-  <si>
-    <t>ベアリング（軸受）</t>
-  </si>
-  <si>
-    <t>ベアリング</t>
-  </si>
-  <si>
-    <t>Bearing</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>wheel-hub</t>
-  </si>
-  <si>
-    <t>ホイールハブ</t>
-  </si>
-  <si>
-    <t>Wheel Hub</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
-    <t>bosch</t>
-  </si>
-  <si>
-    <t>ボッシュ</t>
-  </si>
-  <si>
-    <t>Robert Bosch GmbH</t>
-  </si>
-  <si>
-    <t>2026-02-05</t>
-  </si>
-  <si>
     <t>motor-generator</t>
   </si>
   <si>
-    <t>モータージェネレーター（MG）</t>
-  </si>
-  <si>
     <t>モータージェネレーター</t>
   </si>
   <si>
     <t>Motor Generator</t>
   </si>
   <si>
-    <t>2026-01-28</t>
-  </si>
-  <si>
     <t>regenerative-braking</t>
   </si>
   <si>
@@ -1196,39 +839,6 @@
     <t>Regenerative Braking</t>
   </si>
   <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
-    <t>sumitomo-wiring</t>
-  </si>
-  <si>
-    <t>住友電装</t>
-  </si>
-  <si>
-    <t>スミトモデンソウ</t>
-  </si>
-  <si>
-    <t>Sumitomo Wiring Systems, Ltd.</t>
-  </si>
-  <si>
-    <t>2026-02-09</t>
-  </si>
-  <si>
-    <t>catalytic-converter</t>
-  </si>
-  <si>
-    <t>触媒コンバーター（三元触媒）</t>
-  </si>
-  <si>
-    <t>ショクバイコンバーター</t>
-  </si>
-  <si>
-    <t>Catalytic Converter</t>
-  </si>
-  <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
     <t>direct-injection</t>
   </si>
   <si>
@@ -1238,70 +848,7 @@
     <t>チョクフンエンジン</t>
   </si>
   <si>
-    <t>Direct Injection Engine</t>
-  </si>
-  <si>
-    <t>2026-01-26</t>
-  </si>
-  <si>
-    <t>power-split-device</t>
-  </si>
-  <si>
-    <t>動力分割機構</t>
-  </si>
-  <si>
-    <t>ドウリョクブンカツキコウ</t>
-  </si>
-  <si>
-    <t>Power Split Device</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>astemo</t>
-  </si>
-  <si>
-    <t>日立Astemo（アステモ）</t>
-  </si>
-  <si>
-    <t>アステモ</t>
-  </si>
-  <si>
-    <t>Hitachi Astemo, Ltd.</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>honda</t>
-  </si>
-  <si>
-    <t>本田技研工業（ホンダ）</t>
-  </si>
-  <si>
-    <t>ホンダ</t>
-  </si>
-  <si>
-    <t>Honda Motor Co., Ltd.</t>
-  </si>
-  <si>
-    <t>2026-02-11</t>
-  </si>
-  <si>
-    <t>yazaki</t>
-  </si>
-  <si>
-    <t>矢崎総業</t>
-  </si>
-  <si>
-    <t>ヤザキソウギョウ</t>
-  </si>
-  <si>
-    <t>Yazaki Corporation</t>
-  </si>
-  <si>
-    <t>2026-02-01</t>
+    <t>Direct Injection</t>
   </si>
   <si>
     <t>planetary-gear</t>
@@ -1316,9 +863,6 @@
     <t>Planetary Gear Set</t>
   </si>
   <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
     <t>1958-agreement</t>
   </si>
   <si>
@@ -1331,16 +875,25 @@
     <t>センキュウヒャクゴジュウハチネンキョウテイ</t>
   </si>
   <si>
-    <t>UNECE 1958 Agreement</t>
-  </si>
-  <si>
-    <t>2026-02-27</t>
+    <t>Agreement of 1958 (UNECE)</t>
+  </si>
+  <si>
+    <t>agves</t>
+  </si>
+  <si>
+    <t>AGVES</t>
+  </si>
+  <si>
+    <t>エージーブイイーエス</t>
+  </si>
+  <si>
+    <t>Advisory Group on Vehicle-Environment-Safety</t>
   </si>
   <si>
     <t>gtr</t>
   </si>
   <si>
-    <t>GTR（世界技術規則）</t>
+    <t>GTR</t>
   </si>
   <si>
     <t>ジーティーアール</t>
@@ -1349,6 +902,42 @@
     <t>Global Technical Regulation</t>
   </si>
   <si>
+    <t>kvms</t>
+  </si>
+  <si>
+    <t>KVMS</t>
+  </si>
+  <si>
+    <t>ケーブイエムエス</t>
+  </si>
+  <si>
+    <t>Known Vulnerability Management System</t>
+  </si>
+  <si>
+    <t>nhtsa</t>
+  </si>
+  <si>
+    <t>NHTSA</t>
+  </si>
+  <si>
+    <t>エヌエイチティーエスエー</t>
+  </si>
+  <si>
+    <t>National Highway Traffic Safety Administration</t>
+  </si>
+  <si>
+    <t>rxswin</t>
+  </si>
+  <si>
+    <t>RxSWIN</t>
+  </si>
+  <si>
+    <t>アールエックススウィン</t>
+  </si>
+  <si>
+    <t>Rx Software Identification Number</t>
+  </si>
+  <si>
     <t>un-r100</t>
   </si>
   <si>
@@ -1358,70 +947,7 @@
     <t>ユーエヌアールヒャク</t>
   </si>
   <si>
-    <t>UN Regulation No. 100 (Electric Power Train)</t>
-  </si>
-  <si>
-    <t>2026-02-17</t>
-  </si>
-  <si>
-    <t>un-r13h</t>
-  </si>
-  <si>
-    <t>UN R13-H</t>
-  </si>
-  <si>
-    <t>ユーエヌアールジュウサンエイチ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 13-H (Braking of M1 vehicles)</t>
-  </si>
-  <si>
-    <t>2026-02-13</t>
-  </si>
-  <si>
-    <t>un-r137</t>
-  </si>
-  <si>
-    <t>UN R137</t>
-  </si>
-  <si>
-    <t>ユーエヌアールヒャクサンジュウナナ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 137 (Frontal Impact - Pole)</t>
-  </si>
-  <si>
-    <t>2026-02-18</t>
-  </si>
-  <si>
-    <t>un-r151</t>
-  </si>
-  <si>
-    <t>UN R151</t>
-  </si>
-  <si>
-    <t>ユーエヌアールヒャクゴジュウイチ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 151 (BSIS - Blind Spot Information System)</t>
-  </si>
-  <si>
-    <t>2026-02-19</t>
-  </si>
-  <si>
-    <t>un-r152</t>
-  </si>
-  <si>
-    <t>UN R152</t>
-  </si>
-  <si>
-    <t>ユーエヌアールヒャクゴジュウニ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 152 (AEBS - M1/N1)</t>
-  </si>
-  <si>
-    <t>2026-02-20</t>
+    <t>UN Regulation No.100 (EV Safety)</t>
   </si>
   <si>
     <t>un-r155</t>
@@ -1430,13 +956,10 @@
     <t>UN R155</t>
   </si>
   <si>
-    <t>ユーエヌアールヒャクゴジュウゴ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 155 (Cyber Security)</t>
-  </si>
-  <si>
-    <t>2026-02-21</t>
+    <t>ユーエヌアールイチゴーゴー</t>
+  </si>
+  <si>
+    <t>UN Regulation No.155 (Cyber Security)</t>
   </si>
   <si>
     <t>un-r156</t>
@@ -1445,10 +968,10 @@
     <t>UN R156</t>
   </si>
   <si>
-    <t>ユーエヌアールヒャクゴジュウロク</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 156 (Software Update)</t>
+    <t>ユーエヌアールイチゴーロク</t>
+  </si>
+  <si>
+    <t>UN Regulation No.156 (Software Update)</t>
   </si>
   <si>
     <t>un-r157</t>
@@ -1457,103 +980,28 @@
     <t>UN R157</t>
   </si>
   <si>
-    <t>ユーエヌアールヒャクゴジュウナナ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 157 (ALKS - Automated Lane Keeping System)</t>
-  </si>
-  <si>
-    <t>2026-02-23</t>
-  </si>
-  <si>
-    <t>un-r158</t>
-  </si>
-  <si>
-    <t>UN R158</t>
-  </si>
-  <si>
-    <t>ユーエヌアールヒャクゴジュウハチ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 158 (Reversing motion / REI)</t>
-  </si>
-  <si>
-    <t>un-r160</t>
-  </si>
-  <si>
-    <t>UN R160</t>
-  </si>
-  <si>
-    <t>ユーエヌアールヒャクロクジュウ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 160 (EDR - Event Data Recorder)</t>
-  </si>
-  <si>
-    <t>2026-02-25</t>
-  </si>
-  <si>
-    <t>un-r79</t>
-  </si>
-  <si>
-    <t>UN R79</t>
-  </si>
-  <si>
-    <t>ユーエヌアールナナジュウキュウ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 79 (Steering Equipment)</t>
-  </si>
-  <si>
-    <t>2026-02-14</t>
-  </si>
-  <si>
-    <t>un-r94</t>
-  </si>
-  <si>
-    <t>UN R94</t>
-  </si>
-  <si>
-    <t>ユーエヌアールキュウジュウヨン</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 94 (Frontal Collision)</t>
-  </si>
-  <si>
-    <t>2026-02-15</t>
-  </si>
-  <si>
-    <t>un-r95</t>
-  </si>
-  <si>
-    <t>UN R95</t>
-  </si>
-  <si>
-    <t>ユーエヌアールキュウジュウゴ</t>
-  </si>
-  <si>
-    <t>UN Regulation No. 95 (Lateral Collision)</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
+    <t>ユーエヌアールイチゴーナナ</t>
+  </si>
+  <si>
+    <t>UN Regulation No.157 (ALKS)</t>
   </si>
   <si>
     <t>wltp</t>
   </si>
   <si>
-    <t>WLTP（世界統一試験手法）</t>
+    <t>WLTP</t>
   </si>
   <si>
     <t>ダブリューエルティーピー</t>
   </si>
   <si>
-    <t>Worldwide harmonized Light vehicles Test Procedure</t>
+    <t>Worldwide Harmonized Light Vehicles Test Procedure</t>
   </si>
   <si>
     <t>wp29</t>
   </si>
   <si>
-    <t>WP.29（自動車基準調和世界フォーラム）</t>
+    <t>WP.29</t>
   </si>
   <si>
     <t>ダブリューピーニジュウキュウ</t>
@@ -1562,13 +1010,10 @@
     <t>World Forum for Harmonization of Vehicle Regulations</t>
   </si>
   <si>
-    <t>2026-02-12</t>
-  </si>
-  <si>
     <t>type-approval</t>
   </si>
   <si>
-    <t>型式認可（タイプアプルーバル）</t>
+    <t>型式認可</t>
   </si>
   <si>
     <t>カタシキニンカ</t>
@@ -1577,6 +1022,18 @@
     <t>Type Approval</t>
   </si>
   <si>
+    <t>china-gb</t>
+  </si>
+  <si>
+    <t>中国GB規格</t>
+  </si>
+  <si>
+    <t>チュウゴクジービーキカク</t>
+  </si>
+  <si>
+    <t>China GB Standards (Guobiao)</t>
+  </si>
+  <si>
     <t>記事数</t>
   </si>
   <si>
@@ -1587,9 +1044,6 @@
   </si>
   <si>
     <t>要修正</t>
-  </si>
-  <si>
-    <t>その他</t>
   </si>
   <si>
     <t>合計</t>
@@ -2010,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O106"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2142,7 +1596,7 @@
         <v>25</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>21</v>
@@ -2174,22 +1628,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>21</v>
@@ -2221,22 +1675,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>21</v>
@@ -2268,22 +1722,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>21</v>
@@ -2315,22 +1769,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>21</v>
@@ -2362,22 +1816,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>21</v>
@@ -2409,22 +1863,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>21</v>
@@ -2456,22 +1910,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>21</v>
@@ -2503,22 +1957,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>21</v>
@@ -2550,22 +2004,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>21</v>
@@ -2597,22 +2051,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>21</v>
@@ -2644,22 +2098,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>21</v>
@@ -2691,22 +2145,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>21</v>
@@ -2738,22 +2192,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>21</v>
@@ -2785,22 +2239,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>21</v>
@@ -2832,22 +2286,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>21</v>
@@ -2879,22 +2333,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>21</v>
@@ -2926,22 +2380,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>21</v>
@@ -2973,22 +2427,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>21</v>
@@ -3020,22 +2474,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>21</v>
@@ -3067,22 +2521,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>21</v>
@@ -3114,22 +2568,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>21</v>
@@ -3161,22 +2615,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>21</v>
@@ -3208,22 +2662,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>21</v>
@@ -3255,22 +2709,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>21</v>
@@ -3302,22 +2756,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>21</v>
@@ -3349,22 +2803,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>152</v>
+        <v>115</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>156</v>
+        <v>20</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>21</v>
@@ -3396,22 +2850,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>157</v>
+        <v>117</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>21</v>
@@ -3443,22 +2897,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>21</v>
@@ -3490,22 +2944,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>170</v>
+        <v>129</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>21</v>
@@ -3537,22 +2991,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>21</v>
@@ -3584,22 +3038,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>21</v>
@@ -3631,22 +3085,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>186</v>
+        <v>20</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>21</v>
@@ -3678,22 +3132,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>21</v>
@@ -3725,22 +3179,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>21</v>
@@ -3772,22 +3226,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>200</v>
-      </c>
       <c r="G38" s="4" t="s">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="H38" s="4" t="s">
         <v>21</v>
@@ -3819,22 +3273,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>21</v>
@@ -3866,22 +3320,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>207</v>
+        <v>158</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>21</v>
@@ -3913,22 +3367,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>21</v>
@@ -3960,22 +3414,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>216</v>
+        <v>166</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>218</v>
+        <v>123</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>219</v>
+        <v>167</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>220</v>
+        <v>168</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>221</v>
+        <v>20</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>21</v>
@@ -4007,22 +3461,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>226</v>
+        <v>20</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>21</v>
@@ -4054,22 +3508,22 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>229</v>
+        <v>176</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>230</v>
+        <v>177</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>21</v>
@@ -4101,22 +3555,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>232</v>
+        <v>178</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>233</v>
+        <v>179</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>21</v>
@@ -4148,22 +3602,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>237</v>
+        <v>182</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>238</v>
+        <v>183</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>241</v>
+        <v>20</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>21</v>
@@ -4195,22 +3649,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>21</v>
@@ -4242,22 +3696,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>249</v>
+        <v>192</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>251</v>
+        <v>20</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>21</v>
@@ -4289,22 +3743,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>252</v>
+        <v>194</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>21</v>
+        <v>197</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>21</v>
@@ -4336,22 +3790,22 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>256</v>
+        <v>198</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>258</v>
+        <v>200</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>259</v>
+        <v>201</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>21</v>
@@ -4383,22 +3837,22 @@
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>21</v>
@@ -4430,22 +3884,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>269</v>
+        <v>209</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>21</v>
@@ -4477,22 +3931,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>271</v>
+        <v>210</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>273</v>
+        <v>211</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>274</v>
+        <v>212</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>275</v>
+        <v>20</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>21</v>
@@ -4524,22 +3978,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>276</v>
+        <v>213</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>277</v>
+        <v>214</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>278</v>
+        <v>214</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>279</v>
+        <v>215</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>280</v>
+        <v>20</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>21</v>
@@ -4571,22 +4025,22 @@
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>281</v>
+        <v>216</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>282</v>
+        <v>217</v>
       </c>
       <c r="D55" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>283</v>
-      </c>
       <c r="F55" s="6" t="s">
-        <v>284</v>
+        <v>219</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>21</v>
@@ -4618,22 +4072,22 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>286</v>
+        <v>220</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>287</v>
+        <v>221</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>288</v>
+        <v>221</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>21</v>
@@ -4665,22 +4119,22 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>291</v>
+        <v>224</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>292</v>
+        <v>225</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>292</v>
+        <v>225</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>293</v>
+        <v>226</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>294</v>
+        <v>20</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>21</v>
@@ -4712,22 +4166,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>295</v>
+        <v>227</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>296</v>
+        <v>228</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>296</v>
+        <v>229</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>297</v>
+        <v>230</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>298</v>
+        <v>20</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>21</v>
@@ -4759,22 +4213,22 @@
         <v>58</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>299</v>
+        <v>231</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>300</v>
+        <v>232</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>301</v>
+        <v>234</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>21</v>
@@ -4806,22 +4260,22 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>304</v>
+        <v>236</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>305</v>
+        <v>238</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>307</v>
+        <v>20</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>21</v>
@@ -4853,22 +4307,22 @@
         <v>60</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>308</v>
+        <v>240</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>309</v>
+        <v>241</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>309</v>
+        <v>242</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>21</v>
@@ -4900,22 +4354,22 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>312</v>
+        <v>244</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>313</v>
+        <v>245</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>313</v>
+        <v>246</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>314</v>
+        <v>247</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="H62" s="4" t="s">
         <v>21</v>
@@ -4947,22 +4401,22 @@
         <v>62</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>316</v>
+        <v>248</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>317</v>
+        <v>249</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>317</v>
+        <v>250</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>318</v>
+        <v>251</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>319</v>
+        <v>20</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>21</v>
@@ -4994,22 +4448,22 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>320</v>
+        <v>252</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>321</v>
+        <v>253</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>321</v>
+        <v>254</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>322</v>
+        <v>255</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>323</v>
+        <v>20</v>
       </c>
       <c r="H64" s="4" t="s">
         <v>21</v>
@@ -5041,22 +4495,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>324</v>
+        <v>256</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>325</v>
+        <v>257</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>325</v>
+        <v>257</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>326</v>
+        <v>258</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>21</v>
@@ -5088,22 +4542,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>328</v>
+        <v>259</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>329</v>
+        <v>260</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>329</v>
+        <v>260</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>330</v>
+        <v>261</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="H66" s="4" t="s">
         <v>21</v>
@@ -5135,22 +4589,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>332</v>
+        <v>262</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>333</v>
+        <v>263</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>333</v>
+        <v>263</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>334</v>
+        <v>264</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>335</v>
+        <v>20</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>21</v>
@@ -5182,22 +4636,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>336</v>
+        <v>265</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>337</v>
+        <v>266</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>340</v>
+        <v>20</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>21</v>
@@ -5229,22 +4683,22 @@
         <v>68</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>341</v>
+        <v>268</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>342</v>
+        <v>269</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>343</v>
+        <v>269</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>344</v>
+        <v>270</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>345</v>
+        <v>20</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>21</v>
@@ -5276,22 +4730,22 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>346</v>
+        <v>271</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>348</v>
+        <v>273</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>349</v>
+        <v>274</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>21</v>
@@ -5323,22 +4777,22 @@
         <v>70</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>351</v>
+        <v>275</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>352</v>
+        <v>276</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>352</v>
+        <v>277</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>353</v>
+        <v>278</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>21</v>
@@ -5370,22 +4824,22 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>355</v>
+        <v>279</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>356</v>
+        <v>280</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>357</v>
+        <v>281</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>21</v>
@@ -5417,22 +4871,22 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>360</v>
+        <v>283</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>361</v>
+        <v>284</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>361</v>
+        <v>286</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>362</v>
+        <v>287</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>21</v>
@@ -5464,22 +4918,22 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>365</v>
+        <v>289</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>366</v>
+        <v>291</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>367</v>
+        <v>20</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>21</v>
@@ -5511,22 +4965,22 @@
         <v>74</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>368</v>
+        <v>292</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>369</v>
+        <v>293</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>369</v>
+        <v>294</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>370</v>
+        <v>295</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>371</v>
+        <v>20</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>21</v>
@@ -5558,22 +5012,22 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>372</v>
+        <v>296</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>373</v>
+        <v>297</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>374</v>
+        <v>298</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>375</v>
+        <v>299</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>21</v>
@@ -5605,22 +5059,22 @@
         <v>76</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>377</v>
+        <v>300</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>378</v>
+        <v>301</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>379</v>
+        <v>303</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>21</v>
@@ -5652,22 +5106,22 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>381</v>
+        <v>304</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>382</v>
+        <v>305</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>382</v>
+        <v>306</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>383</v>
+        <v>307</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>21</v>
@@ -5699,22 +5153,22 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>385</v>
+        <v>308</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>386</v>
+        <v>309</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>387</v>
+        <v>310</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>388</v>
+        <v>311</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>21</v>
@@ -5746,22 +5200,22 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>390</v>
+        <v>312</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>391</v>
+        <v>313</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>392</v>
+        <v>314</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>393</v>
+        <v>315</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>21</v>
@@ -5793,22 +5247,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>395</v>
+        <v>316</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>396</v>
+        <v>317</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>397</v>
+        <v>318</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>398</v>
+        <v>319</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>399</v>
+        <v>20</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>21</v>
@@ -5840,22 +5294,22 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>401</v>
+        <v>321</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>402</v>
+        <v>322</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>403</v>
+        <v>323</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>404</v>
+        <v>20</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>21</v>
@@ -5887,22 +5341,22 @@
         <v>82</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>405</v>
+        <v>324</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>406</v>
+        <v>325</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>407</v>
+        <v>326</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>408</v>
+        <v>327</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>409</v>
+        <v>20</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>21</v>
@@ -5934,22 +5388,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>410</v>
+        <v>328</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>411</v>
+        <v>329</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>412</v>
+        <v>330</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>413</v>
+        <v>331</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>414</v>
+        <v>20</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>21</v>
@@ -5981,22 +5435,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>415</v>
+        <v>332</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>416</v>
+        <v>333</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>417</v>
+        <v>334</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>418</v>
+        <v>335</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>21</v>
@@ -6028,22 +5482,22 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>420</v>
+        <v>336</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>421</v>
+        <v>337</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>422</v>
+        <v>338</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>423</v>
+        <v>339</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>424</v>
+        <v>20</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>21</v>
@@ -6070,959 +5524,19 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
-        <v>86</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N87" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O87" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="4">
-        <v>87</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="G88" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="H88" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K88" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L88" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M88" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N88" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O88" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="89" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
-        <v>88</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="G89" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N89" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O89" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="4">
-        <v>89</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M90" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N90" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O90" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
-        <v>90</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O91" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="4">
-        <v>91</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L92" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M92" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N92" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O92" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
-        <v>92</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>457</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>459</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K93" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M93" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N93" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O93" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="4">
-        <v>93</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L94" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M94" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N94" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O94" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
-        <v>94</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>467</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="G95" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M95" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N95" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O95" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="4">
-        <v>95</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L96" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M96" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N96" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O96" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="97" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
-        <v>96</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M97" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N97" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O97" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="4">
-        <v>97</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>480</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N98" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O98" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
-        <v>98</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>485</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="G99" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N99" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O99" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
-        <v>99</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O100" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="6">
-        <v>100</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="G101" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J101" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K101" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L101" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M101" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N101" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O101" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="4">
-        <v>101</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="D102" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="F102" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I102" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J102" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K102" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L102" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N102" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O102" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
-        <v>102</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="G103" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L103" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M103" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N103" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O103" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="4">
-        <v>103</v>
-      </c>
-      <c r="B104" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="D104" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E104" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="F104" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K104" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M104" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N104" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O104" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
-        <v>104</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="G105" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N105" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O105" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="4">
-        <v>105</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>517</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I106" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J106" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K106" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L106" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M106" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N106" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="O106" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O106"/>
+  <autoFilter ref="A1:O86"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="H10:M106">
+    <dataValidation type="list" allowBlank="1" sqref="H10:M86">
       <formula1>"OK,NG,—"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:M106">
+    <dataValidation type="list" allowBlank="1" sqref="H2:M86">
       <formula1>"OK,NG,—"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N10:N106">
+    <dataValidation type="list" allowBlank="1" sqref="N10:N86">
       <formula1>"合格,要修正,未レビュー"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N106">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N86">
       <formula1>"合格,要修正,未レビュー"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7033,7 +5547,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -7047,24 +5561,24 @@
         <v>3</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>521</v>
+        <v>340</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>522</v>
+        <v>341</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>523</v>
+        <v>342</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>524</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>525</v>
+        <v>69</v>
       </c>
       <c r="B2">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -7078,10 +5592,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>233</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -7095,7 +5609,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B4">
         <v>13</v>
@@ -7112,10 +5626,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>437</v>
+        <v>285</v>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7129,10 +5643,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7146,10 +5660,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>526</v>
+        <v>222</v>
       </c>
       <c r="B7">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -7158,6 +5672,40 @@
         <v>0</v>
       </c>
       <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B9">
+        <v>85</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>0</v>
       </c>
     </row>

--- a/docs/review-checklist.xlsx
+++ b/docs/review-checklist.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="393">
   <si>
     <t>No.</t>
   </si>
@@ -59,25 +59,49 @@
     <t>指摘事項・コメント</t>
   </si>
   <si>
+    <t>ccu</t>
+  </si>
+  <si>
+    <t>CCU</t>
+  </si>
+  <si>
+    <t>自動車部品</t>
+  </si>
+  <si>
+    <t>シーシーユー</t>
+  </si>
+  <si>
+    <t>Central/Connectivity Control Unit</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>cv-joint</t>
   </si>
   <si>
     <t>CVジョイント</t>
   </si>
   <si>
-    <t>自動車部品</t>
-  </si>
-  <si>
     <t>シーブイジョイント</t>
   </si>
   <si>
     <t>Constant Velocity Joint</t>
   </si>
   <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t/>
+    <t>dcm</t>
+  </si>
+  <si>
+    <t>DCM</t>
+  </si>
+  <si>
+    <t>ディーシーエム</t>
+  </si>
+  <si>
+    <t>Data Communication Module</t>
   </si>
   <si>
     <t>ecu</t>
@@ -215,15 +239,27 @@
     <t>Three-Way Catalytic Converter</t>
   </si>
   <si>
+    <t>auto-isac</t>
+  </si>
+  <si>
+    <t>Auto-ISAC</t>
+  </si>
+  <si>
+    <t>サイバーセキュリティ</t>
+  </si>
+  <si>
+    <t>オートアイサック</t>
+  </si>
+  <si>
+    <t>Automotive Information Sharing and Analysis Center</t>
+  </si>
+  <si>
     <t>csms</t>
   </si>
   <si>
     <t>CSMS</t>
   </si>
   <si>
-    <t>サイバーセキュリティ</t>
-  </si>
-  <si>
     <t>シーエスエムエス</t>
   </si>
   <si>
@@ -266,6 +302,30 @@
     <t>ISO/SAE 21434 Road Vehicles - Cybersecurity Engineering</t>
   </si>
   <si>
+    <t>j-auto-isac</t>
+  </si>
+  <si>
+    <t>J-Auto-ISAC</t>
+  </si>
+  <si>
+    <t>ジェイオートアイサック</t>
+  </si>
+  <si>
+    <t>Japan Automotive ISAC</t>
+  </si>
+  <si>
+    <t>jasic</t>
+  </si>
+  <si>
+    <t>JASIC</t>
+  </si>
+  <si>
+    <t>ジャシック</t>
+  </si>
+  <si>
+    <t>Japan Automotive Security Information Center</t>
+  </si>
+  <si>
     <t>pki</t>
   </si>
   <si>
@@ -278,6 +338,18 @@
     <t>Public Key Infrastructure</t>
   </si>
   <si>
+    <t>sbom</t>
+  </si>
+  <si>
+    <t>SBOM</t>
+  </si>
+  <si>
+    <t>エスボム</t>
+  </si>
+  <si>
+    <t>Software Bill of Materials</t>
+  </si>
+  <si>
     <t>secoc</t>
   </si>
   <si>
@@ -326,6 +398,18 @@
     <t>VLAN Separation</t>
   </si>
   <si>
+    <t>wpa</t>
+  </si>
+  <si>
+    <t>WPA2/WPA3</t>
+  </si>
+  <si>
+    <t>ダブリューピーエーツースリー</t>
+  </si>
+  <si>
+    <t>Wi-Fi Protected Access 2/3</t>
+  </si>
+  <si>
     <t>secure-ota</t>
   </si>
   <si>
@@ -620,6 +704,18 @@
     <t>ISO 26262 Road Vehicles - Functional Safety</t>
   </si>
   <si>
+    <t>qnx</t>
+  </si>
+  <si>
+    <t>QNX</t>
+  </si>
+  <si>
+    <t>キューエヌエックス</t>
+  </si>
+  <si>
+    <t>QNX Neutrino RTOS</t>
+  </si>
+  <si>
     <t>severity</t>
   </si>
   <si>
@@ -662,6 +758,18 @@
     <t>Safety Goal</t>
   </si>
   <si>
+    <t>ipc</t>
+  </si>
+  <si>
+    <t>プロセス間通信（IPC）</t>
+  </si>
+  <si>
+    <t>プロセスカンツウシン</t>
+  </si>
+  <si>
+    <t>Inter-Process Communication</t>
+  </si>
+  <si>
     <t>freedom-from-interference</t>
   </si>
   <si>
@@ -902,6 +1010,30 @@
     <t>Global Technical Regulation</t>
   </si>
   <si>
+    <t>jaspar</t>
+  </si>
+  <si>
+    <t>JASPAR</t>
+  </si>
+  <si>
+    <t>ジャスパー</t>
+  </si>
+  <si>
+    <t>Japan Automotive Software Platform and Architecture</t>
+  </si>
+  <si>
+    <t>jsae</t>
+  </si>
+  <si>
+    <t>JSAE（自動車技術会）</t>
+  </si>
+  <si>
+    <t>ジェイサエ</t>
+  </si>
+  <si>
+    <t>Society of Automotive Engineers of Japan</t>
+  </si>
+  <si>
     <t>kvms</t>
   </si>
   <si>
@@ -1008,6 +1140,18 @@
   </si>
   <si>
     <t>World Forum for Harmonization of Vehicle Regulations</t>
+  </si>
+  <si>
+    <t>process-approval</t>
+  </si>
+  <si>
+    <t>プロセス認可</t>
+  </si>
+  <si>
+    <t>プロセスニンカ</t>
+  </si>
+  <si>
+    <t>Process Approval (A-SPICE Assessment)</t>
   </si>
   <si>
     <t>type-approval</t>
@@ -1464,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1684,10 +1828,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>20</v>
@@ -1722,19 +1866,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>20</v>
@@ -1769,19 +1913,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>20</v>
@@ -1816,19 +1960,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
@@ -1863,19 +2007,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>20</v>
@@ -1910,19 +2054,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
@@ -1957,19 +2101,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>20</v>
@@ -2004,19 +2148,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
@@ -2051,19 +2195,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>20</v>
@@ -2098,19 +2242,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
@@ -2145,19 +2289,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>20</v>
@@ -2192,19 +2336,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>20</v>
@@ -2239,19 +2383,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>20</v>
@@ -2286,19 +2430,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>20</v>
@@ -2333,13 +2477,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>78</v>
@@ -2386,7 +2530,7 @@
         <v>81</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>82</v>
@@ -2433,7 +2577,7 @@
         <v>85</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>86</v>
@@ -2480,7 +2624,7 @@
         <v>89</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>90</v>
@@ -2527,7 +2671,7 @@
         <v>93</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>94</v>
@@ -2574,7 +2718,7 @@
         <v>97</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>98</v>
@@ -2621,7 +2765,7 @@
         <v>101</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>102</v>
@@ -2668,7 +2812,7 @@
         <v>105</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>106</v>
@@ -2715,13 +2859,13 @@
         <v>109</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>20</v>
@@ -2756,19 +2900,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>20</v>
@@ -2803,19 +2947,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>20</v>
@@ -2850,19 +2994,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>20</v>
@@ -2897,19 +3041,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>20</v>
@@ -2944,19 +3088,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>20</v>
@@ -2991,19 +3135,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>20</v>
@@ -3038,19 +3182,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>20</v>
@@ -3085,13 +3229,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>140</v>
@@ -3138,13 +3282,13 @@
         <v>143</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="E36" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>20</v>
@@ -3179,19 +3323,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="D37" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="6" t="s">
+      <c r="F37" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>149</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>20</v>
@@ -3226,13 +3370,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>152</v>
@@ -3279,7 +3423,7 @@
         <v>155</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>156</v>
@@ -3326,7 +3470,7 @@
         <v>159</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>160</v>
@@ -3373,7 +3517,7 @@
         <v>163</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>164</v>
@@ -3420,13 +3564,13 @@
         <v>167</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>20</v>
@@ -3461,13 +3605,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>172</v>
@@ -3514,7 +3658,7 @@
         <v>175</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>176</v>
@@ -3561,7 +3705,7 @@
         <v>179</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>180</v>
@@ -3608,7 +3752,7 @@
         <v>183</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>184</v>
@@ -3655,7 +3799,7 @@
         <v>187</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>188</v>
@@ -3702,7 +3846,7 @@
         <v>191</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>192</v>
@@ -3749,13 +3893,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E49" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F49" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>20</v>
@@ -3790,13 +3934,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>171</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>200</v>
@@ -3843,7 +3987,7 @@
         <v>203</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="E51" s="6" t="s">
         <v>204</v>
@@ -3890,7 +4034,7 @@
         <v>207</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>208</v>
@@ -3937,13 +4081,13 @@
         <v>211</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>20</v>
@@ -3978,19 +4122,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>20</v>
@@ -4025,19 +4169,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>20</v>
@@ -4072,19 +4216,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>20</v>
@@ -4119,19 +4263,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>20</v>
@@ -4166,19 +4310,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>20</v>
@@ -4213,19 +4357,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>20</v>
@@ -4260,19 +4404,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>20</v>
@@ -4307,19 +4451,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>20</v>
@@ -4354,13 +4498,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>246</v>
@@ -4407,7 +4551,7 @@
         <v>249</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>250</v>
@@ -4454,7 +4598,7 @@
         <v>253</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>254</v>
@@ -4501,13 +4645,13 @@
         <v>257</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>257</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>20</v>
@@ -4542,19 +4686,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>20</v>
@@ -4589,19 +4733,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>20</v>
@@ -4636,19 +4780,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>20</v>
@@ -4683,19 +4827,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C69" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>233</v>
-      </c>
       <c r="E69" s="6" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>20</v>
@@ -4730,19 +4874,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>20</v>
@@ -4777,19 +4921,19 @@
         <v>70</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>20</v>
@@ -4824,19 +4968,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>20</v>
@@ -4871,19 +5015,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>20</v>
@@ -4918,19 +5062,19 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>20</v>
@@ -4965,19 +5109,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>20</v>
@@ -5012,19 +5156,19 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>20</v>
@@ -5059,13 +5203,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>302</v>
@@ -5112,13 +5256,13 @@
         <v>305</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="E78" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>20</v>
@@ -5153,19 +5297,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C79" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="D79" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D79" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E79" s="6" t="s">
+      <c r="F79" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>311</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>20</v>
@@ -5200,19 +5344,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="D80" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E80" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="E80" s="4" t="s">
+      <c r="F80" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>20</v>
@@ -5247,19 +5391,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="D81" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E81" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="D81" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E81" s="6" t="s">
+      <c r="F81" s="6" t="s">
         <v>318</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>319</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>20</v>
@@ -5294,13 +5438,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C82" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="D82" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>285</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>322</v>
@@ -5347,7 +5491,7 @@
         <v>325</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>326</v>
@@ -5394,7 +5538,7 @@
         <v>329</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>330</v>
@@ -5441,7 +5585,7 @@
         <v>333</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="E85" s="6" t="s">
         <v>334</v>
@@ -5488,7 +5632,7 @@
         <v>337</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>338</v>
@@ -5524,19 +5668,583 @@
         <v>21</v>
       </c>
     </row>
+    <row r="87" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4">
+        <v>87</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N88" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O88" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <v>89</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4">
+        <v>91</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O92" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4">
+        <v>93</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="G94" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N95" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O95" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O96" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>96</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="K97" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <v>97</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="G98" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O98" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O86"/>
+  <autoFilter ref="A1:O98"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="H10:M86">
+    <dataValidation type="list" allowBlank="1" sqref="H10:M98">
       <formula1>"OK,NG,—"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:M86">
+    <dataValidation type="list" allowBlank="1" sqref="H2:M98">
       <formula1>"OK,NG,—"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N10:N86">
+    <dataValidation type="list" allowBlank="1" sqref="N10:N98">
       <formula1>"合格,要修正,未レビュー"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="N2:N86">
+    <dataValidation type="list" allowBlank="1" sqref="N2:N98">
       <formula1>"合格,要修正,未レビュー"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5561,24 +6269,24 @@
         <v>3</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>340</v>
+        <v>388</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>342</v>
+        <v>390</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>343</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -5592,7 +6300,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="B3">
         <v>14</v>
@@ -5609,10 +6317,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5626,10 +6334,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -5646,7 +6354,7 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5660,7 +6368,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -5677,7 +6385,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="B8">
         <v>12</v>
@@ -5694,10 +6402,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>344</v>
+        <v>392</v>
       </c>
       <c r="B9">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C9">
         <v>0</v>
